--- a/filer/20213094_lagekage.xlsx
+++ b/filer/20213094_lagekage.xlsx
@@ -7542,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7651,22 +7651,20 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
+          <t>fsa:SharePremium</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
+          <t>fsa:SharePremium</t>
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="G4" s="38" t="n">
         <v>0</v>
@@ -7686,57 +7684,24 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:SharePremium</t>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:SharePremium</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="35" t="n"/>
+        <v>1661</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>-4241</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n">
-        <v>1661</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>-4241</v>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/20213094_lagekage.xlsx
+++ b/filer/20213094_lagekage.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/20213094_lagekage.xlsx
+++ b/filer/20213094_lagekage.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1531,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3009,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4343,19 +4343,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4461,19 +4461,19 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -4771,6 +4771,13 @@
       <c r="F98" s="13">
         <f>IFERROR($F$36/($F$61+$F$67)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4802,19 +4809,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4824,19 +4831,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>830222</v>
+        <v>905220</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>905220</v>
+        <v>1011785</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1011785</v>
+        <v>1068558</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1068558</v>
+        <v>1122500</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1122500</v>
+        <v>1229709</v>
       </c>
     </row>
     <row r="3">
@@ -4846,19 +4853,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>5932</v>
+        <v>479</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>5</v>
+        <v>692</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>692</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="4">
@@ -4868,19 +4875,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>212107</v>
+        <v>230582</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>230582</v>
+        <v>286918</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>286918</v>
+        <v>305211</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>305211</v>
+        <v>297030</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>297030</v>
+        <v>323718</v>
       </c>
     </row>
     <row r="5">
@@ -4890,19 +4897,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>245797</v>
+        <v>265646</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>265646</v>
+        <v>316166</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>316166</v>
+        <v>315990</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>315990</v>
+        <v>325447</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>325447</v>
+        <v>342282</v>
       </c>
     </row>
     <row r="6">
@@ -4912,19 +4919,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>378250</v>
+        <v>409471</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>409471</v>
+        <v>408701</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>408701</v>
+        <v>447362</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>447362</v>
+        <v>500715</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>500715</v>
+        <v>564960</v>
       </c>
     </row>
     <row r="7">
@@ -4934,19 +4941,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>393095</v>
+        <v>382891</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>382891</v>
+        <v>411274</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>411274</v>
+        <v>414647</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>414647</v>
+        <v>440567</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>440567</v>
+        <v>481947</v>
       </c>
     </row>
     <row r="8">
@@ -4963,19 +4970,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>82876</v>
+        <v>72658</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>72658</v>
+        <v>73238</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>73238</v>
+        <v>74466</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>74466</v>
+        <v>67934</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>67934</v>
+        <v>65318</v>
       </c>
     </row>
     <row r="10">
@@ -4985,19 +4992,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>73079</v>
+        <v>26510</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>26510</v>
+        <v>65952</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>65952</v>
+        <v>87173</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>87173</v>
+        <v>73485</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>73485</v>
+        <v>42143</v>
       </c>
     </row>
     <row r="11">
@@ -5007,19 +5014,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-170800</v>
+        <v>-72588</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-72588</v>
+        <v>-141763</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-141763</v>
+        <v>-128924</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-128924</v>
+        <v>-81271</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-81271</v>
+        <v>-24448</v>
       </c>
     </row>
     <row r="12">
@@ -5041,19 +5048,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>11667</v>
+        <v>12</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>12</v>
+        <v>1005</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1005</v>
+        <v>53</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>153</v>
+        <v>17398</v>
       </c>
     </row>
     <row r="14">
@@ -5063,19 +5070,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>14968</v>
+        <v>11689</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>11689</v>
+        <v>7239</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>7239</v>
+        <v>13434</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>13434</v>
+        <v>26934</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>26934</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="15">
@@ -5085,19 +5092,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>-3301</v>
+        <v>-11677</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>-11677</v>
+        <v>-6234</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>-6234</v>
+        <v>-13381</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-13381</v>
+        <v>-26781</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>-26781</v>
+        <v>-6406</v>
       </c>
     </row>
     <row r="16">
@@ -5107,19 +5114,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-174101</v>
+        <v>-84265</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>-84265</v>
+        <v>-147997</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>-147997</v>
+        <v>-142305</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-142305</v>
+        <v>-108052</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>-108052</v>
+        <v>-30854</v>
       </c>
     </row>
     <row r="17">
@@ -5129,19 +5136,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>-2800</v>
+        <v>-1900</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>-1900</v>
+        <v>-3123</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>-3123</v>
+        <v>-5708</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-5708</v>
+        <v>-6167</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>-6167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5151,19 +5158,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>-171301</v>
+        <v>-82365</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>-82365</v>
+        <v>-144874</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>-144874</v>
+        <v>-136597</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-136597</v>
+        <v>-101885</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>-101885</v>
+        <v>-30854</v>
       </c>
     </row>
     <row r="19">
@@ -5173,19 +5180,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>948</v>
+        <v>892</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>892</v>
+        <v>932</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>932</v>
+        <v>911</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>917</v>
+        <v>966</v>
       </c>
     </row>
     <row r="20">
@@ -5195,19 +5202,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>41479</v>
+        <v>34324</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>34324</v>
+        <v>49345</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>49345</v>
+        <v>27910</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>27910</v>
+        <v>15460</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>15460</v>
+        <v>51571</v>
       </c>
     </row>
   </sheetData>
@@ -5239,19 +5246,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5261,19 +5268,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>19307</v>
+        <v>28342</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>28342</v>
+        <v>41463</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>41463</v>
+        <v>43594</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>43594</v>
+        <v>37828</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>37828</v>
+        <v>37618</v>
       </c>
     </row>
     <row r="3">
@@ -5295,19 +5302,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>43037</v>
+        <v>36061</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>36061</v>
+        <v>29085</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>29085</v>
+        <v>22352</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>22352</v>
+        <v>16562</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>16562</v>
+        <v>11517</v>
       </c>
     </row>
     <row r="5">
@@ -5317,19 +5324,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>63077</v>
+        <v>64994</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>64994</v>
+        <v>70997</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>70997</v>
+        <v>66253</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>66253</v>
+        <v>54531</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>54531</v>
+        <v>49210</v>
       </c>
     </row>
     <row r="6">
@@ -5351,19 +5358,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>112197</v>
+        <v>108420</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>108420</v>
+        <v>109953</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>109953</v>
+        <v>106784</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>106784</v>
+        <v>99944</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>99944</v>
+        <v>93874</v>
       </c>
     </row>
     <row r="8">
@@ -5373,19 +5380,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>34253</v>
+        <v>29029</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>29029</v>
+        <v>26652</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>26652</v>
+        <v>20655</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>20655</v>
+        <v>14356</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>14356</v>
+        <v>13292</v>
       </c>
     </row>
     <row r="9">
@@ -5395,19 +5402,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>180305</v>
+        <v>161726</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>161726</v>
+        <v>151060</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>151060</v>
+        <v>130610</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>130610</v>
+        <v>106424</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>106424</v>
+        <v>87433</v>
       </c>
     </row>
     <row r="10">
@@ -5417,19 +5424,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>223</v>
+        <v>528</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>552</v>
+        <v>646</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>646</v>
+        <v>1380</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>1380</v>
+        <v>9003</v>
       </c>
     </row>
     <row r="11">
@@ -5439,19 +5446,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>326978</v>
+        <v>299703</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>299703</v>
+        <v>288217</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>288217</v>
+        <v>258695</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>258695</v>
+        <v>222104</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>222104</v>
+        <v>203602</v>
       </c>
     </row>
     <row r="12">
@@ -5473,19 +5480,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>8225</v>
+        <v>7121</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>7121</v>
+        <v>7330</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>7330</v>
+        <v>7987</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>7987</v>
+        <v>7716</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>7716</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="14">
@@ -5495,19 +5502,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>8225</v>
+        <v>7121</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>7121</v>
+        <v>7330</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>7330</v>
+        <v>7987</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>7987</v>
+        <v>7716</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>7716</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="15">
@@ -5517,19 +5524,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>398280</v>
+        <v>371818</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>371818</v>
+        <v>366544</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>366544</v>
+        <v>332935</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>332935</v>
+        <v>284351</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>284351</v>
+        <v>259927</v>
       </c>
     </row>
     <row r="16">
@@ -5539,19 +5546,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>14850</v>
+        <v>14690</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>14690</v>
+        <v>19638</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>19638</v>
+        <v>21033</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>21033</v>
+        <v>20527</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>20527</v>
+        <v>22131</v>
       </c>
     </row>
     <row r="17">
@@ -5573,19 +5580,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>669</v>
+        <v>305</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>305</v>
+        <v>1303</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1303</v>
+        <v>1371</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>1371</v>
+        <v>1338</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>1338</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="19">
@@ -5595,19 +5602,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>15519</v>
+        <v>14995</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>14995</v>
+        <v>20941</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>20941</v>
+        <v>22404</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>22404</v>
+        <v>21865</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>21865</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="20">
@@ -5617,19 +5624,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>3884</v>
+        <v>5090</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>5090</v>
+        <v>6692</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6692</v>
+        <v>6649</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>6649</v>
+        <v>9469</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>9469</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="21">
@@ -5640,12 +5647,14 @@
       </c>
       <c r="B21" s="16" t="n"/>
       <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
+      <c r="D21" s="16" t="n">
+        <v>3233</v>
+      </c>
       <c r="E21" s="16" t="n">
-        <v>3233</v>
+        <v>13567</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>13567</v>
+        <v>26079</v>
       </c>
     </row>
     <row r="22">
@@ -5655,19 +5664,19 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>4313</v>
+        <v>10608</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>10608</v>
+        <v>11616</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>11616</v>
+        <v>8388</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>8388</v>
+        <v>6672</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>6672</v>
+        <v>23143</v>
       </c>
     </row>
     <row r="23">
@@ -5677,19 +5686,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>6547</v>
+        <v>7482</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>7482</v>
+        <v>9645</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>9645</v>
+        <v>8966</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>8966</v>
+        <v>13405</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>13405</v>
+        <v>11076</v>
       </c>
     </row>
     <row r="24">
@@ -5723,19 +5732,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>2800</v>
+        <v>1900</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>1900</v>
+        <v>3123</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>3123</v>
+        <v>5708</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>5708</v>
+        <v>6167</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>6167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5745,19 +5754,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>17544</v>
+        <v>25080</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>25080</v>
+        <v>31076</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>31076</v>
+        <v>32944</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>32944</v>
+        <v>49280</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>49280</v>
+        <v>73548</v>
       </c>
     </row>
     <row r="28">
@@ -5779,19 +5788,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>205577</v>
+        <v>134487</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>134487</v>
+        <v>207218</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>207218</v>
+        <v>239200</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>239200</v>
+        <v>234571</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>234571</v>
+        <v>236146</v>
       </c>
     </row>
     <row r="30">
@@ -5801,19 +5810,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>238640</v>
+        <v>174562</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>174562</v>
+        <v>259235</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>259235</v>
+        <v>294548</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>294548</v>
+        <v>305716</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>305716</v>
+        <v>333017</v>
       </c>
     </row>
     <row r="31">
@@ -5823,19 +5832,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>636920</v>
+        <v>546380</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>546380</v>
+        <v>625779</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>625779</v>
+        <v>627483</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>627483</v>
+        <v>590067</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>590067</v>
+        <v>592944</v>
       </c>
     </row>
     <row r="32">
@@ -5848,7 +5857,7 @@
         <v>1041</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>1041</v>
+        <v>1079</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>1079</v>
@@ -5879,19 +5888,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>15059</v>
+        <v>22106</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>22106</v>
+        <v>32340</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>32340</v>
+        <v>34001</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>34001</v>
+        <v>29760</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>29760</v>
+        <v>29341</v>
       </c>
     </row>
     <row r="35">
@@ -5925,19 +5934,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>302665</v>
+        <v>213253</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>213253</v>
+        <v>258105</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>258105</v>
+        <v>169847</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>169847</v>
+        <v>72203</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>72203</v>
+        <v>166768</v>
       </c>
     </row>
     <row r="38">
@@ -5947,19 +5956,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>318765</v>
+        <v>236400</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>236400</v>
+        <v>291524</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>291524</v>
+        <v>204927</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>204927</v>
+        <v>103042</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>103042</v>
+        <v>197188</v>
       </c>
     </row>
     <row r="39">
@@ -5969,19 +5978,19 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>25365</v>
+        <v>24374</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>24374</v>
+        <v>13756</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>13756</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>13756</v>
+        <v>13151</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>13151</v>
+        <v>13349</v>
       </c>
     </row>
     <row r="40">
@@ -6014,9 +6023,7 @@
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B42" s="16" t="n"/>
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
@@ -6029,14 +6036,12 @@
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>46570</v>
+        <v>67459</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>67459</v>
-      </c>
-      <c r="D43" s="16" t="n">
         <v>55260</v>
       </c>
+      <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
       <c r="F43" s="16" t="n"/>
     </row>
@@ -6047,19 +6052,19 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>46570</v>
+        <v>67459</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>67459</v>
+        <v>55260</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>55260</v>
+        <v>51877</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>51877</v>
+        <v>49963</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>49963</v>
+        <v>48796</v>
       </c>
     </row>
     <row r="45">
@@ -6081,19 +6086,19 @@
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>5961</v>
+        <v>2615</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>2615</v>
+        <v>5024</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>5024</v>
+        <v>2959</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>2959</v>
+        <v>2812</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>2812</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="47">
@@ -6127,19 +6132,19 @@
         </is>
       </c>
       <c r="B49" s="16" t="n">
-        <v>106622</v>
+        <v>119104</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>119104</v>
+        <v>126363</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>126363</v>
+        <v>139195</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>139195</v>
+        <v>123671</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>123671</v>
+        <v>135236</v>
       </c>
     </row>
     <row r="50">
@@ -6149,19 +6154,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>69398</v>
+        <v>27028</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>27028</v>
+        <v>64902</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>64902</v>
+        <v>140876</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>140876</v>
+        <v>234579</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>234579</v>
+        <v>121157</v>
       </c>
     </row>
     <row r="51">
@@ -6207,19 +6212,19 @@
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>64239</v>
+        <v>59036</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>59036</v>
+        <v>60083</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>60083</v>
+        <v>65879</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>65879</v>
+        <v>55869</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>55869</v>
+        <v>66130</v>
       </c>
     </row>
     <row r="55">
@@ -6228,18 +6233,20 @@
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n"/>
+      <c r="B55" s="16" t="n">
+        <v>10364</v>
+      </c>
       <c r="C55" s="16" t="n">
-        <v>10364</v>
+        <v>8867</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>8867</v>
+        <v>8014</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>8014</v>
+        <v>6980</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>6980</v>
+        <v>8508</v>
       </c>
     </row>
     <row r="56">
@@ -6249,19 +6256,19 @@
         </is>
       </c>
       <c r="B56" s="16" t="n">
-        <v>246220</v>
+        <v>218147</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>218147</v>
+        <v>265239</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>265239</v>
+        <v>356923</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>356923</v>
+        <v>423911</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>423911</v>
+        <v>333611</v>
       </c>
     </row>
     <row r="57">
@@ -6271,19 +6278,19 @@
         </is>
       </c>
       <c r="B57" s="16" t="n">
-        <v>292790</v>
+        <v>285606</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>285606</v>
+        <v>320499</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>320499</v>
+        <v>408800</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>408800</v>
+        <v>473874</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>473874</v>
+        <v>382407</v>
       </c>
     </row>
     <row r="58">
@@ -6293,19 +6300,19 @@
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>636920</v>
+        <v>546380</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>546380</v>
+        <v>625779</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>625779</v>
+        <v>627483</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>627483</v>
+        <v>590067</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>590067</v>
+        <v>592944</v>
       </c>
     </row>
   </sheetData>
@@ -6344,13 +6351,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7064,7 +7071,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7182,7 +7189,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7358,7 +7365,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7581,27 +7588,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7627,14 +7634,12 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>1687</v>
+        <v>1457</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>1457</v>
-      </c>
-      <c r="F3" s="35" t="n">
         <v>4625</v>
       </c>
+      <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
@@ -7659,16 +7664,14 @@
           <t>fsa:SharePremium</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7694,12 +7697,14 @@
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+      <c r="F5" s="35" t="n">
+        <v>1661</v>
+      </c>
       <c r="G5" s="35" t="n">
-        <v>1661</v>
+        <v>-4241</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>-4241</v>
+        <v>-419</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
